--- a/threat_logs.xlsx
+++ b/threat_logs.xlsx
@@ -436,16 +436,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>127.0.0.1</t>
+          <t>203.0.113.42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>RFI</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>201</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/threat_logs.xlsx
+++ b/threat_logs.xlsx
@@ -436,16 +436,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>203.0.113.42</t>
+          <t>127.0.0.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RFI</t>
+          <t>SQL Injection</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>85</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/threat_logs.xlsx
+++ b/threat_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,11 +441,86 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SQL Injection</t>
+          <t>XSS - Alert Payload</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>XSS - Cookie Stealing</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XSS - Credential Harvesting</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>XSS - Keylogging</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>XSS - Redirect</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>XSS - Session Hijacking / Data Exfiltration</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
